--- a/reports/report_2026-08-16.xlsx
+++ b/reports/report_2026-08-16.xlsx
@@ -532,7 +532,11 @@
           <t>oveporexton</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Orzeyful</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
@@ -546,7 +550,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14 篇</t>
+          <t>4 篇</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -592,33 +596,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Baxdrostat</t>
+          <t>Bevacizumab</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ASTRAZENECA AB</t>
+          <t>OUTLOOK THERAPEUTICS, INC.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treatment of hypertension in adults</t>
+          <t>Treatment of adult patients with advanced or metastatic cancers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>高血壓 / 三期標靶 / 生物製劑</t>
+          <t>Treatment of adu... / 三期標靶 / 生物製劑</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7 篇</t>
+          <t>231 篇</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Baxdrostat+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Bevacizumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -659,33 +663,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bevacizumab</t>
+          <t>Apixaban</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>OUTLOOK THERAPEUTICS, INC.</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with advanced or metastatic cancers</t>
+          <t>Prevention of venous thromboembolic events (VTE), stroke and systemic embolism; treatment of deep vein thrombosis (DVT) and pulmonary embolism (PE) in adults. Treatment of VTE in children from 28 days to &lt; 18 years of age.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Treatment of adu... / 三期標靶 / 生物製劑</t>
+          <t>缺血性腦中風 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7 篇</t>
+          <t>54 篇</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Bevacizumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Apixaban+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -726,33 +726,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gadoquatrane</t>
+          <t>Orforglipron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BAYER HEALTHCARE</t>
+          <t>ELI LILLY AND CO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>For contrast enhancement in magnetic resonance imaging (MRI) used for adults and paediatric patients of all ages.</t>
+          <t>Treatment of obesity and type 2 diabetes mellitus in adults</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>For contrast enh... / 三期標靶 / 生物製劑</t>
+          <t>第2型糖尿病 / 三期標靶 / 生物製劑</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7 篇</t>
+          <t>27 篇</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Gadoquatrane+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Orforglipron+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,33 +793,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Orforglipron</t>
+          <t>Abatacept</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ELI LILLY AND CO</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Treatment of obesity and type 2 diabetes mellitus in adults</t>
+          <t>Treatment of rheumatoid, psoriatic arthritis and polyarticular juvenile idiopathic arthritis in patients 6 years of age and older</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>第2型糖尿病 / 三期標靶 / 生物製劑</t>
+          <t>類風濕性關節炎 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7 篇</t>
+          <t>24 篇</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Orforglipron+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Abatacept+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -860,33 +856,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Relacorilant</t>
+          <t>Baxdrostat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CORCEPT THERAP</t>
+          <t>ASTRAZENECA AB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with platinum-resistant epithelial ovarian, fallopian tube, or primary peritoneal cancer</t>
+          <t>Treatment of hypertension in adults</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>卵巢癌 / 孤兒藥</t>
+          <t>高血壓 / 三期標靶 / 生物製劑</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7 篇</t>
+          <t>17 篇</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Relacorilant+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Baxdrostat+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -927,29 +923,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sonrotoclax</t>
+          <t>Asundexian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with relapsed or refractory mantle cell lymphoma (MCL)</t>
+          <t>Prevention of ischaemic stroke in adults</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>淋巴瘤 / 三期標靶 / 生物製劑</t>
+          <t>缺血性腦中風 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7 篇</t>
+          <t>16 篇</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Sonrotoclax+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Asundexian+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -990,33 +986,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Veligrotug</t>
+          <t>Atrasentan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VIRIDIAN THERAPEUTICS INC</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Treatment of moderate to severe thyroid eye disease in adults</t>
+          <t>Indicated for the treatment of adults with primary immunoglobulin A nephropathy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Treatment of mod... / 三期標靶 / 生物製劑</t>
+          <t>Indicated for th... / 孤兒藥</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7 篇</t>
+          <t>6 篇</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Veligrotug+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Atrasentan+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1057,29 +1049,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abatacept</t>
+          <t>Bepirovirsen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treatment of rheumatoid, psoriatic arthritis and polyarticular juvenile idiopathic arthritis in patients 6 years of age and older</t>
+          <t>Treatment of chronic hepatitis B virus (HBV) infection in adults</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>類風濕性關節炎 / 新分子實體 (NME)</t>
+          <t>Treatment of chr... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>6 篇</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Abatacept+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Bepirovirsen+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1120,29 +1112,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aceclidine</t>
+          <t>Relacorilant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CORCEPT THERAP</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treatment of presbyopia in adults</t>
+          <t>Treatment of adult patients with platinum-resistant epithelial ovarian, fallopian tube, or primary peritoneal cancer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Treatment of pre... / 新分子實體 (NME)</t>
+          <t>卵巢癌 / 孤兒藥</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>6 篇</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Aceclidine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Relacorilant+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1183,19 +1179,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anselamimab</t>
+          <t>Cemdisiran</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with kappa light chain amyloidosis</t>
+          <t>Treatment of generalised myasthenia gravis in adult patients</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>類澱粉沉積症 / 孤兒藥</t>
+          <t>Treatment of gen... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1205,7 +1201,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Anselamimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cemdisiran+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1246,19 +1242,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Apitegromab</t>
+          <t>Cladribine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Treatment of 5q spinal muscular atrophy (SMA)</t>
+          <t>Treatment of acute myeloid leukaemia (AML) in adults</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>脊髓性肌肉萎縮症 / 孤兒藥</t>
+          <t>白血病 / 孤兒藥</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1268,7 +1264,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Apitegromab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cladribine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1309,19 +1305,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Apixaban</t>
+          <t>Cosibelimab</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prevention of venous thromboembolic events (VTE), stroke and systemic embolism; treatment of deep vein thrombosis (DVT) and pulmonary embolism (PE) in adults. Treatment of VTE in children from 28 days to &lt; 18 years of age.</t>
+          <t>Treatment of adult patients with metastatic or locally advanced cutaneous squamous cell carcinoma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>缺血性腦中風 / 新分子實體 (NME)</t>
+          <t>鱗狀細胞癌 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1331,7 +1327,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Apixaban+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cosibelimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1372,19 +1368,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Asundexian</t>
+          <t>Denecimig</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prevention of ischaemic stroke in adults</t>
+          <t>Prophylaxis of bleeding episodes in patients with haemophilia A</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>缺血性腦中風 / 新分子實體 (NME)</t>
+          <t>Prophylaxis of b... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1394,7 +1390,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Asundexian+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Denecimig+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1435,19 +1431,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atrasentan</t>
+          <t>Denosumab</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Indicated for the treatment of adults with primary immunoglobulin A nephropathy</t>
+          <t>Treatment of adult patients with osteoporosis or bone loss</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Indicated for th... / 孤兒藥</t>
+          <t>骨質疏鬆症 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1457,7 +1453,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Atrasentan+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Denosumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1498,19 +1494,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bepirovirsen</t>
+          <t>Deucrictibant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treatment of chronic hepatitis B virus (HBV) infection in adults</t>
+          <t>Treatment of acute attacks of hereditary angioedema (HAE) in adult and paediatric patients 12 years of age and older</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Treatment of chr... / 新分子實體 (NME)</t>
+          <t>遺傳性血管水腫 / 孤兒藥</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1520,7 +1516,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Bepirovirsen+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Deucrictibant+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1561,19 +1557,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bilayer engineered skin composed of autologous keratinocytes and allogeneic fibroblasts embedded in an allogeneic plasma matrix</t>
+          <t>Deuruxolitinib</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Treatment of adults and children with partial deep dermal and full-thickness burns.</t>
+          <t>Treatment of severe alopecia areata in adults</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>深度燒傷 / 孤兒藥</t>
+          <t>Treatment of sev... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1583,7 +1579,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Bilayer%20engineered%20skin%20composed%20of%20autologous%20keratinocytes%20and%20allogeneic%20fibroblasts%20embedded%20in%20an%20allogeneic%20plasma%20matrix+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Deuruxolitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1624,19 +1620,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cefepime / Zidebactam</t>
+          <t>Doravirine / Islatravir</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Treatment of a number of infections in adults</t>
+          <t>Treatment of HIV-1 infection in adults</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Treatment of a n... / 新分子實體 (NME)</t>
+          <t>HIV-1 感染 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1646,7 +1642,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cefepime%20/%20Zidebactam+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Doravirine%20/%20Islatravir+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1687,19 +1683,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cemdisiran</t>
+          <t>Emapalumab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Treatment of generalised myasthenia gravis in adult patients</t>
+          <t>Treatment of acute or recurrent secondary haemophagocytic lymphohistiocytosis (sHLH) in adult and paediatric patients (6 months and older)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treatment of gen... / 新分子實體 (NME)</t>
+          <t>Treatment of acu... / 孤兒藥</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1709,7 +1705,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cemdisiran+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Emapalumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1750,19 +1746,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cladribine</t>
+          <t>Enlicitide</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Treatment of acute myeloid leukaemia (AML) in adults</t>
+          <t>Indicated in adults with primary hypercholesterolaemia or mixed dyslipidaemia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>白血病 / 孤兒藥</t>
+          <t>Indicated in adu... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1772,7 +1768,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cladribine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Enlicitide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1813,19 +1809,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cosibelimab</t>
+          <t>Ensartinib</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with metastatic or locally advanced cutaneous squamous cell carcinoma</t>
+          <t>The treatment of adult patients with anaplastic lymphoma kinase (ALK)-positive advanced non-small cell lung cancer (NSCLC).</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>鱗狀細胞癌 / 新分子實體 (NME)</t>
+          <t>非小細胞肺癌 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1835,7 +1831,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cosibelimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ensartinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1876,19 +1872,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Denecimig</t>
+          <t>Etripamil</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prophylaxis of bleeding episodes in patients with haemophilia A</t>
+          <t>Indicated for the rapid conversion of paroxysmal supraventricular tachycardia (PSVT) episodes to sinus rhythm in adults.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Prophylaxis of b... / 新分子實體 (NME)</t>
+          <t>脊髓性肌肉萎縮症 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1898,7 +1894,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Denecimig+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Etripamil+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1939,19 +1935,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Denosumab</t>
+          <t>Filgrastim</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with osteoporosis or bone loss</t>
+          <t>Treatment of neutropenia in adults and children</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>骨質疏鬆症 / 新分子實體 (NME)</t>
+          <t>Treatment of neu... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1961,7 +1957,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Denosumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Filgrastim+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2002,19 +1998,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deucrictibant</t>
+          <t>Fondaparinux sodium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treatment of acute attacks of hereditary angioedema (HAE) in adult and paediatric patients 12 years of age and older</t>
+          <t>Prevention of venous thromboembolic events (VTE), treatment of deep vein thrombosis (DVT), treatment of pulmonary embolism, treatment of unstable angina and myocardial infarction in adults</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>遺傳性血管水腫 / 孤兒藥</t>
+          <t>Prevention of ve... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2024,7 +2020,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Deucrictibant+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Fondaparinux%20sodium+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2065,19 +2061,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deuruxolitinib</t>
+          <t>Garetosmab</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Treatment of severe alopecia areata in adults</t>
+          <t>Treatment of adult patients with fibrodysplasia ossificans progressiva (FOP)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treatment of sev... / 新分子實體 (NME)</t>
+          <t>Treatment of adu... / 孤兒藥</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2087,7 +2083,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Deuruxolitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Garetosmab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2128,19 +2124,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Doravirine / Islatravir</t>
+          <t>Gefurulimab</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Treatment of HIV-1 infection in adults</t>
+          <t>Treatment of adult patients with generalised myasthemia gravis (gMG)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HIV-1 感染 / 新分子實體 (NME)</t>
+          <t>Treatment of adu... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2150,7 +2146,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Doravirine%20/%20Islatravir+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Gefurulimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2191,19 +2187,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Emapalumab</t>
+          <t>Glepaglutide</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treatment of acute or recurrent secondary haemophagocytic lymphohistiocytosis (sHLH) in adult and paediatric patients (6 months and older)</t>
+          <t>Treatment of adults with Short Bowel Syndrome</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treatment of acu... / 孤兒藥</t>
+          <t>Treatment of adu... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2213,7 +2209,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Emapalumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Glepaglutide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2254,19 +2250,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Enlicitide</t>
+          <t>Hexaminolevulinate</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Indicated in adults with primary hypercholesterolaemia or mixed dyslipidaemia</t>
+          <t>Treatment of adult patients with histologically confirmed cervical high-grade squamous intraepithelial lesions (HSIL)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Indicated in adu... / 新分子實體 (NME)</t>
+          <t>Treatment of adu... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2276,7 +2272,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Enlicitide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Hexaminolevulinate+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2317,19 +2313,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ensartinib</t>
+          <t>Human IgG1 monoclonal antibody against insulin like growth factor-1 receptor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The treatment of adult patients with anaplastic lymphoma kinase (ALK)-positive advanced non-small cell lung cancer (NSCLC).</t>
+          <t>Treatment of thyroid eye disease (TED) in adults</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>非小細胞肺癌 / 新分子實體 (NME)</t>
+          <t>Treatment of thy... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2339,7 +2335,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ensartinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Human%20IgG1%20monoclonal%20antibody%20against%20insulin%20like%20growth%20factor-1%20receptor+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2380,19 +2376,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Etripamil</t>
+          <t>Ianalumab</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Indicated for the rapid conversion of paroxysmal supraventricular tachycardia (PSVT) episodes to sinus rhythm in adults.</t>
+          <t>Treatment of Sjögren’s disease in adults</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>脊髓性肌肉萎縮症 / 新分子實體 (NME)</t>
+          <t>Treatment of Sjö... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2402,7 +2398,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Etripamil+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ianalumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2443,19 +2439,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Filgrastim</t>
+          <t>Influenza mRNA vaccine</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Treatment of neutropenia in adults and children</t>
+          <t>Immunisation for the prevention of influenza disease in adults</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Treatment of neu... / 新分子實體 (NME)</t>
+          <t>Immunisation for... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2465,7 +2461,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Filgrastim+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Influenza%20mRNA%20vaccine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2506,19 +2502,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fondaparinux sodium</t>
+          <t>Insulin aspart</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Prevention of venous thromboembolic events (VTE), treatment of deep vein thrombosis (DVT), treatment of pulmonary embolism, treatment of unstable angina and myocardial infarction in adults</t>
+          <t>Treatment of diabetes mellitus from 1 year of age</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Prevention of ve... / 新分子實體 (NME)</t>
+          <t>第2型糖尿病 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2528,7 +2524,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Fondaparinux%20sodium+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Insulin%20aspart+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2569,19 +2565,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Garetosmab</t>
+          <t>Japanese Encephalitis Chimeric Vaccine Substipharm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with fibrodysplasia ossificans progressiva (FOP)</t>
+          <t>Immunisation against Japanese encephalitis in adults, adolescents, children and infants aged 9 months and older</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Treatment of adu... / 孤兒藥</t>
+          <t>Immunisation aga... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2591,7 +2587,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Garetosmab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Japanese%20Encephalitis%20Chimeric%20Vaccine%20Substipharm+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2632,14 +2628,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gefurulimab</t>
+          <t>Lemborexant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with generalised myasthemia gravis (gMG)</t>
+          <t>Treatment of adult patients with insomnia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2654,7 +2650,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Gefurulimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Lemborexant+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2695,19 +2691,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Glepaglutide</t>
+          <t>Lunsotogene parvec</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Treatment of adults with Short Bowel Syndrome</t>
+          <t>Treatment of biallelic OTOF variant-associated hearing loss in adults and children</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Treatment of adu... / 新分子實體 (NME)</t>
+          <t>Treatment of bia... / 孤兒藥</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2717,7 +2713,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Glepaglutide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Lunsotogene%20parvec+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2758,19 +2754,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hexaminolevulinate</t>
+          <t>Mezigdomide</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with histologically confirmed cervical high-grade squamous intraepithelial lesions (HSIL)</t>
+          <t>Treatment of relapsed or refractory multiple myeloma in adults</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treatment of adu... / 新分子實體 (NME)</t>
+          <t>Treatment of rel... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2780,7 +2776,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Hexaminolevulinate+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Mezigdomide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2821,19 +2817,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Human IgG1 monoclonal antibody against insulin like growth factor-1 receptor</t>
+          <t>Molgramostim</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treatment of thyroid eye disease (TED) in adults</t>
+          <t>Treatment of pulmonary alveolar proteinosis in adults</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Treatment of thy... / 新分子實體 (NME)</t>
+          <t>Treatment of pul... / 孤兒藥</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2843,7 +2839,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Human%20IgG1%20monoclonal%20antibody%20against%20insulin%20like%20growth%20factor-1%20receptor+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Molgramostim+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2884,19 +2880,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ianalumab</t>
+          <t>Norucholic acid</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treatment of Sjögren’s disease in adults</t>
+          <t>Treatment of primary sclerosing cholangitis (PSC) in adults.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treatment of Sjö... / 新分子實體 (NME)</t>
+          <t>Treatment of pri... / 孤兒藥</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2906,7 +2902,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ianalumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Norucholic%20acid+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2947,19 +2943,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Influenza mRNA vaccine</t>
+          <t>Olanzapine</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Immunisation for the prevention of influenza disease in adults</t>
+          <t>Treatment of schizophrenia in adults</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Immunisation for... / 新分子實體 (NME)</t>
+          <t>Treatment of sch... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2969,7 +2965,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Influenza%20mRNA%20vaccine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Olanzapine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3010,19 +3006,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Insulin aspart</t>
+          <t>Omalizumab</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treatment of diabetes mellitus from 1 year of age</t>
+          <t>Treatment of asthma, chronic rhinosinusitis with nasal polyps (CRSwNP) and chronic spontaneous urticaria (CSU)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第2型糖尿病 / 新分子實體 (NME)</t>
+          <t>嚴重氣喘 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3032,7 +3028,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Insulin%20aspart+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Omalizumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3073,19 +3069,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Japanese Encephalitis Chimeric Vaccine Substipharm</t>
+          <t>Pertuzumab</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Immunisation against Japanese encephalitis in adults, adolescents, children and infants aged 9 months and older</t>
+          <t>Treatment of breast cancer in adults</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Immunisation aga... / 新分子實體 (NME)</t>
+          <t>乳癌 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3095,7 +3091,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Japanese%20Encephalitis%20Chimeric%20Vaccine%20Substipharm+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Pertuzumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3136,19 +3132,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lemborexant</t>
+          <t>Pimicotinib</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Treatment of adult patients with insomnia</t>
+          <t>Treatment of tenosynovial giant cell tumour in adults and adolescents from 12 years of age</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Treatment of adu... / 新分子實體 (NME)</t>
+          <t>Treatment of ten... / 孤兒藥</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3158,7 +3154,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Lemborexant+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Pimicotinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3199,19 +3195,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lunsotogene parvec</t>
+          <t>Ponatinib</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treatment of biallelic OTOF variant-associated hearing loss in adults and children</t>
+          <t>Treatment of chronic myeloid leukaemia (CML) or Philadelphia chromosome positive acute lymphoblastic leukaemia (Ph+ ALL) in adults</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Treatment of bia... / 孤兒藥</t>
+          <t>白血病 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3221,7 +3217,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Lunsotogene%20parvec+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ponatinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3262,19 +3258,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mezigdomide</t>
+          <t>Povorcitinib</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treatment of relapsed or refractory multiple myeloma in adults</t>
+          <t>Treatment of active moderate to severe hidradenitis suppurativa (acne inversa) in adults</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Treatment of rel... / 新分子實體 (NME)</t>
+          <t>Treatment of act... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3284,7 +3280,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Mezigdomide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Povorcitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3325,19 +3321,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Molgramostim</t>
+          <t>Rabies vaccine for human use prepared in cell cultures</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Treatment of pulmonary alveolar proteinosis in adults</t>
+          <t>Pre-exposure and post-exposure prophylaxis against rabies in all age groups</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Treatment of pul... / 孤兒藥</t>
+          <t>Pre-exposure and... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Molgramostim+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Rabies%20vaccine%20for%20human%20use%20prepared%20in%20cell%20cultures+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3388,19 +3384,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Navepegritide</t>
+          <t>Regadenoson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Treatment of achondroplasia in children</t>
+          <t>Pharmacological stress agent for myocardial perfusion imaging (MPI) and measurement of fractional flow reserve (FFR) in adults</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Treatment of ach... / 孤兒藥</t>
+          <t>Pharmacological ... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3410,7 +3406,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Navepegritide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Regadenoson+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3451,19 +3447,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Norucholic acid</t>
+          <t>Rezvilutamide</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Treatment of primary sclerosing cholangitis (PSC) in adults.</t>
+          <t>Treatment of high-volume metastatic hormone-sensitive prostate cancer (mHSPC) in adults</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Treatment of pri... / 孤兒藥</t>
+          <t>攝護腺癌 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3473,7 +3469,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Norucholic%20acid+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Rezvilutamide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3514,19 +3510,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Olanzapine</t>
+          <t>Ruxolitinib</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Treatment of schizophrenia in adults</t>
+          <t>Treatment of myelofibrosis (MF) in adults, treatment of polycythaemia vera (PV) in adults and treatment of Graft versus host disease (GvHD) in adults and children</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Treatment of sch... / 新分子實體 (NME)</t>
+          <t>骨髓纖維化 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3536,7 +3532,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Olanzapine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ruxolitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3577,19 +3573,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Omalizumab</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Treatment of asthma, chronic rhinosinusitis with nasal polyps (CRSwNP) and chronic spontaneous urticaria (CSU)</t>
+          <t>Treatment of type 2 diabetes in adults</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>嚴重氣喘 / 新分子實體 (NME)</t>
+          <t>第2型糖尿病 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3599,7 +3595,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Omalizumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Semaglutide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3640,19 +3636,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pertuzumab</t>
+          <t>Senaparib</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Treatment of breast cancer in adults</t>
+          <t>Maintenance treatment of advanced epithelial high-grade ovarian, fallopian tube or primary peritoneal cancer</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>乳癌 / 新分子實體 (NME)</t>
+          <t>卵巢癌 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3662,7 +3658,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Pertuzumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Senaparib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3703,19 +3699,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pimicotinib</t>
+          <t>Sintilimab</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Treatment of tenosynovial giant cell tumour in adults and adolescents from 12 years of age</t>
+          <t>Treatment of non-squamous non-small cell lung cancer in adults</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Treatment of ten... / 孤兒藥</t>
+          <t>非小細胞肺癌 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3725,7 +3721,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Pimicotinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Sintilimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3766,19 +3762,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ponatinib</t>
+          <t>Sonrotoclax</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Treatment of chronic myeloid leukaemia (CML) or Philadelphia chromosome positive acute lymphoblastic leukaemia (Ph+ ALL) in adults</t>
+          <t>Treatment of adult patients with relapsed or refractory mantle cell lymphoma (MCL)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>白血病 / 新分子實體 (NME)</t>
+          <t>淋巴瘤 / 三期標靶 / 生物製劑</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3788,7 +3784,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ponatinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Sonrotoclax+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3829,19 +3825,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Povorcitinib</t>
+          <t>Taletrectinib</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Treatment of active moderate to severe hidradenitis suppurativa (acne inversa) in adults</t>
+          <t>Treatment of adults with ROS1 positive advanced non-small cell lung cancer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Treatment of act... / 新分子實體 (NME)</t>
+          <t>非小細胞肺癌 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3851,7 +3847,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Povorcitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Taletrectinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3892,19 +3888,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rabies vaccine for human use prepared in cell cultures</t>
+          <t>Tanruprubart</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pre-exposure and post-exposure prophylaxis against rabies in all age groups</t>
+          <t>Treatment of Guillain-Barré syndrome in adults and children</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pre-exposure and... / 新分子實體 (NME)</t>
+          <t>Treatment of Gui... / 孤兒藥</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3914,7 +3910,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Rabies%20vaccine%20for%20human%20use%20prepared%20in%20cell%20cultures+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Tanruprubart+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3955,19 +3951,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Regadenoson</t>
+          <t>Temozolomide</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pharmacological stress agent for myocardial perfusion imaging (MPI) and measurement of fractional flow reserve (FFR) in adults</t>
+          <t>Treatment of adults with glioblastoma multiforme and children with malignant glioma</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pharmacological ... / 新分子實體 (NME)</t>
+          <t>Treatment of adu... / 孤兒藥</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3977,7 +3973,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Regadenoson+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Temozolomide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4018,19 +4014,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rezvilutamide</t>
+          <t>Tofacitinib</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Treatment of high-volume metastatic hormone-sensitive prostate cancer (mHSPC) in adults</t>
+          <t>Treatment of rheumatoid arthritis, psoriatic arthritis, ankylosing spondylitis, and ulcerative colitis in adults, and juvenile idiopathic arthritis (JIA) in children from 2 years old</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>攝護腺癌 / 新分子實體 (NME)</t>
+          <t>類風濕性關節炎 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4040,7 +4036,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Rezvilutamide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Tofacitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4081,19 +4077,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ruxolitinib</t>
+          <t>Tozorakimab</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Treatment of myelofibrosis (MF) in adults, treatment of polycythaemia vera (PV) in adults and treatment of Graft versus host disease (GvHD) in adults and children</t>
+          <t>Treatment for chronic obstructive pulmonary disease (COPD) in adult patients</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>骨髓纖維化 / 新分子實體 (NME)</t>
+          <t>慢性阻塞性肺病 / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4103,7 +4099,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Ruxolitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Tozorakimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4144,19 +4140,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>Vedolizumab</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Treatment of type 2 diabetes in adults</t>
+          <t>Treatment of Ulcerative Colitis, Crohn’s Disease and pouchitis in adults</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>第2型糖尿病 / 新分子實體 (NME)</t>
+          <t>Treatment of Ulc... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4166,7 +4162,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Semaglutide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Vedolizumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4207,19 +4203,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Senaparib</t>
+          <t>Venglustat</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Maintenance treatment of advanced epithelial high-grade ovarian, fallopian tube or primary peritoneal cancer</t>
+          <t>Treatment of Type 3 Gaucher disease (GD3) in adults and children</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>卵巢癌 / 新分子實體 (NME)</t>
+          <t>Treatment of Typ... / 孤兒藥</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4229,7 +4225,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Senaparib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Venglustat+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4270,19 +4266,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sintilimab</t>
+          <t>Zamtocabtagene autoleucel</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Treatment of non-squamous non-small cell lung cancer in adults</t>
+          <t>Treatment of adults with large B-cell lymphoma</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>非小細胞肺癌 / 新分子實體 (NME)</t>
+          <t>淋巴瘤 / 孤兒藥</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4292,7 +4288,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Sintilimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Zamtocabtagene%20autoleucel+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4333,19 +4329,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Taletrectinib</t>
+          <t>Zopapogene imadenovec</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Treatment of adults with ROS1 positive advanced non-small cell lung cancer</t>
+          <t>Treatment of respiratory papillomatosis in adults</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>非小細胞肺癌 / 新分子實體 (NME)</t>
+          <t>Treatment of res... / 孤兒藥</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4355,7 +4351,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Taletrectinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Zopapogene%20imadenovec+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4396,29 +4392,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tanruprubart</t>
+          <t>Apitegromab</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Treatment of Guillain-Barré syndrome in adults and children</t>
+          <t>Treatment of 5q spinal muscular atrophy (SMA)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Treatment of Gui... / 孤兒藥</t>
+          <t>脊髓性肌肉萎縮症 / 孤兒藥</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>3 篇</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Tanruprubart+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Apitegromab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4459,29 +4455,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Temozolomide</t>
+          <t>Gadoquatrane</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BAYER HEALTHCARE</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Treatment of adults with glioblastoma multiforme and children with malignant glioma</t>
+          <t>For contrast enhancement in magnetic resonance imaging (MRI) used for adults and paediatric patients of all ages.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Treatment of adu... / 孤兒藥</t>
+          <t>For contrast enh... / 三期標靶 / 生物製劑</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>3 篇</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Temozolomide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Gadoquatrane+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4522,29 +4522,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tofacitinib</t>
+          <t>Anselamimab</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Treatment of rheumatoid arthritis, psoriatic arthritis, ankylosing spondylitis, and ulcerative colitis in adults, and juvenile idiopathic arthritis (JIA) in children from 2 years old</t>
+          <t>Treatment of adult patients with kappa light chain amyloidosis</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>類風濕性關節炎 / 新分子實體 (NME)</t>
+          <t>類澱粉沉積症 / 孤兒藥</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>2 篇</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Tofacitinib+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Anselamimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4585,29 +4585,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tozorakimab</t>
+          <t>Cefepime / Zidebactam</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Treatment for chronic obstructive pulmonary disease (COPD) in adult patients</t>
+          <t>Treatment of a number of infections in adults</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>慢性阻塞性肺病 / 新分子實體 (NME)</t>
+          <t>Treatment of a n... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>2 篇</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Tozorakimab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Cefepime%20/%20Zidebactam+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4648,29 +4648,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vedolizumab</t>
+          <t>Navepegritide</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Treatment of Ulcerative Colitis, Crohn’s Disease and pouchitis in adults</t>
+          <t>Treatment of achondroplasia in children</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Treatment of Ulc... / 新分子實體 (NME)</t>
+          <t>Treatment of ach... / 孤兒藥</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>2 篇</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Vedolizumab+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Navepegritide+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4711,29 +4711,33 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Venglustat</t>
+          <t>Veligrotug</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VIRIDIAN THERAPEUTICS INC</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Treatment of Type 3 Gaucher disease (GD3) in adults and children</t>
+          <t>Treatment of moderate to severe thyroid eye disease in adults</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Treatment of Typ... / 孤兒藥</t>
+          <t>Treatment of mod... / 三期標靶 / 生物製劑</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>2 篇</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Venglustat+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Veligrotug+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4774,29 +4778,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Zamtocabtagene autoleucel</t>
+          <t>Aceclidine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Treatment of adults with large B-cell lymphoma</t>
+          <t>Treatment of presbyopia in adults</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>淋巴瘤 / 孤兒藥</t>
+          <t>Treatment of pre... / 新分子實體 (NME)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>0 篇</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Zamtocabtagene%20autoleucel+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Aceclidine+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4837,29 +4841,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zopapogene imadenovec</t>
+          <t>Bilayer engineered skin composed of autologous keratinocytes and allogeneic fibroblasts embedded in an allogeneic plasma matrix</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Treatment of respiratory papillomatosis in adults</t>
+          <t>Treatment of adults and children with partial deep dermal and full-thickness burns.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Treatment of res... / 孤兒藥</t>
+          <t>深度燒傷 / 孤兒藥</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4 篇</t>
+          <t>0 篇</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Zopapogene%20imadenovec+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/?term=Bilayer%20engineered%20skin%20composed%20of%20autologous%20keratinocytes%20and%20allogeneic%20fibroblasts%20embedded%20in%20an%20allogeneic%20plasma%20matrix+AND+(Phase+3+OR+%22Phase+III%22+OR+%22clinical+trial%22)+AND+(%22last+1+years%22%5BPDat%5D)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
